--- a/public/downloads/BaeumerTuning2020.xlsx
+++ b/public/downloads/BaeumerTuning2020.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
@@ -659,10 +682,10 @@
         <v>51</v>
       </c>
       <c r="N3" s="5">
-        <v>519.0964193344116</v>
+        <v>519096.4193344116</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03514532290686605</v>
+        <v>35.14532290686606</v>
       </c>
       <c r="P3" s="5">
         <v>14770</v>
@@ -709,10 +732,10 @@
         <v>51</v>
       </c>
       <c r="N4" s="5">
-        <v>1132.482585430145</v>
+        <v>1132482.585430145</v>
       </c>
       <c r="O4" s="4">
-        <v>0.08534799799759932</v>
+        <v>85.34799799759932</v>
       </c>
       <c r="P4" s="5">
         <v>13269</v>
@@ -759,10 +782,10 @@
         <v>51</v>
       </c>
       <c r="N5" s="5">
-        <v>2009.877454280853</v>
+        <v>2009877.454280853</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1415306988438035</v>
+        <v>141.5306988438035</v>
       </c>
       <c r="P5" s="5">
         <v>14201</v>
@@ -809,10 +832,10 @@
         <v>51</v>
       </c>
       <c r="N6" s="5">
-        <v>1617.914328098297</v>
+        <v>1617914.328098297</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09268528460691436</v>
+        <v>92.68528460691437</v>
       </c>
       <c r="P6" s="5">
         <v>17456</v>
@@ -859,10 +882,10 @@
         <v>51</v>
       </c>
       <c r="N7" s="5">
-        <v>5033.968827486038</v>
+        <v>5033968.827486038</v>
       </c>
       <c r="O7" s="4">
-        <v>0.3471463228388413</v>
+        <v>347.1463228388413</v>
       </c>
       <c r="P7" s="5">
         <v>14501</v>
@@ -909,10 +932,10 @@
         <v>51</v>
       </c>
       <c r="N8" s="5">
-        <v>376.919801235199</v>
+        <v>376919.801235199</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02277048276658001</v>
+        <v>22.77048276658001</v>
       </c>
       <c r="P8" s="5">
         <v>16553</v>
@@ -959,10 +982,10 @@
         <v>51</v>
       </c>
       <c r="N9" s="5">
-        <v>596.5886831283569</v>
+        <v>596588.6831283569</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03486987451799386</v>
+        <v>34.86987451799386</v>
       </c>
       <c r="P9" s="5">
         <v>17109</v>
@@ -1009,10 +1032,10 @@
         <v>51</v>
       </c>
       <c r="N10" s="5">
-        <v>1660.018185853958</v>
+        <v>1660018.185853958</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08540506178185718</v>
+        <v>85.40506178185719</v>
       </c>
       <c r="P10" s="5">
         <v>19437</v>
@@ -1059,10 +1082,10 @@
         <v>51</v>
       </c>
       <c r="N11" s="5">
-        <v>558.7461543083191</v>
+        <v>558746.1543083191</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04804352143665684</v>
+        <v>48.04352143665684</v>
       </c>
       <c r="P11" s="5">
         <v>11630</v>
@@ -1109,10 +1132,10 @@
         <v>51</v>
       </c>
       <c r="N12" s="5">
-        <v>360.0205881595612</v>
+        <v>360020.5881595612</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02626928771685963</v>
+        <v>26.26928771685963</v>
       </c>
       <c r="P12" s="5">
         <v>13705</v>
@@ -1159,10 +1182,10 @@
         <v>51</v>
       </c>
       <c r="N13" s="5">
-        <v>966.1607208251953</v>
+        <v>966160.7208251953</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07616560668704732</v>
+        <v>76.16560668704732</v>
       </c>
       <c r="P13" s="5">
         <v>12685</v>
@@ -1209,10 +1232,10 @@
         <v>51</v>
       </c>
       <c r="N14" s="5">
-        <v>6288.193200588226</v>
+        <v>6288193.200588226</v>
       </c>
       <c r="O14" s="4">
-        <v>0.5020914404813339</v>
+        <v>502.0914404813339</v>
       </c>
       <c r="P14" s="5">
         <v>12524</v>
@@ -1259,10 +1282,10 @@
         <v>51</v>
       </c>
       <c r="N15" s="5">
-        <v>5882.067153215408</v>
+        <v>5882067.153215408</v>
       </c>
       <c r="O15" s="4">
-        <v>0.5158802975982641</v>
+        <v>515.8802975982642</v>
       </c>
       <c r="P15" s="5">
         <v>11402</v>
@@ -1309,10 +1332,10 @@
         <v>51</v>
       </c>
       <c r="N16" s="5">
-        <v>1137.669828653336</v>
+        <v>1137669.828653336</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1069439583242466</v>
+        <v>106.9439583242466</v>
       </c>
       <c r="P16" s="5">
         <v>10638</v>
@@ -1359,10 +1382,10 @@
         <v>51</v>
       </c>
       <c r="N17" s="5">
-        <v>1487.499842643738</v>
+        <v>1487499.842643738</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1114065190715801</v>
+        <v>111.4065190715801</v>
       </c>
       <c r="P17" s="5">
         <v>13352</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3653631372020086</v>
+        <v>0.376148285109726</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3752936043790452</v>
+        <v>0.3492376250800563</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4092503064487294</v>
+        <v>0.4205956319043509</v>
       </c>
       <c r="E3" s="4">
-        <v>85.60468631897207</v>
+        <v>76.43990929705224</v>
       </c>
       <c r="F3" s="4">
-        <v>84.255530698482</v>
+        <v>58.23079791200577</v>
       </c>
       <c r="G3" s="5">
         <v>18</v>
       </c>
       <c r="H3" s="5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3394530233922035</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1582858346731369</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1446135462814576</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7989524991063961</v>
+        <v>0.7870588959260357</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3796275587593145</v>
+        <v>0.6586366635667295</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4308874009279463</v>
+        <v>0.7045941021963328</v>
       </c>
       <c r="E4" s="4">
-        <v>79.0096038415371</v>
+        <v>73.45138055222137</v>
       </c>
       <c r="F4" s="4">
-        <v>71.78378734044063</v>
+        <v>54.75128306356228</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
+        <v>7</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.6586366635667295</v>
+      </c>
+      <c r="O4" s="5">
         <v>6</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
+      <c r="P4" s="4">
+        <v>0.5390914925380139</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09128535151654778</v>
+      </c>
+      <c r="R4" s="5">
         <v>6</v>
       </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6135847610860728</v>
+        <v>0.5693141169157028</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6446041548837099</v>
+        <v>0.5806747116628879</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6822487656906147</v>
+        <v>0.6077986728382027</v>
       </c>
       <c r="E5" s="4">
-        <v>84.14115646258507</v>
+        <v>77.39370748299307</v>
       </c>
       <c r="F5" s="4">
-        <v>80.64387583892545</v>
+        <v>60.00069910514471</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5806747116628879</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3314936286942565</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2030960436603548</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,81 +1797,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4205360274305537</v>
+        <v>0.6158839136395208</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3597487605794202</v>
+        <v>0.6342039573270242</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4865530249734028</v>
+        <v>0.6923904223607664</v>
       </c>
       <c r="E3" s="4">
-        <v>84.29705215419509</v>
+        <v>71.15268329554043</v>
       </c>
       <c r="F3" s="4">
-        <v>74.09209545115553</v>
+        <v>60.75192642306679</v>
       </c>
       <c r="G3" s="5">
         <v>18</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.6342039573270242</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2438838286614613</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2009519805218631</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9071826894305722</v>
+        <v>1.086005537270964</v>
       </c>
       <c r="C4" s="4">
-        <v>0.507370411171842</v>
+        <v>1.102131863901128</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5935208850388124</v>
+        <v>1.078677262181763</v>
       </c>
       <c r="E4" s="4">
-        <v>76.76070428171302</v>
+        <v>64.61184473789527</v>
       </c>
       <c r="F4" s="4">
-        <v>62.64903276746878</v>
+        <v>50.56388998552374</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>7</v>
@@ -1755,40 +1915,56 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.086005537270964</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.102131863901128</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7690340203399706</v>
+        <v>0.9158898097213899</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7151851425864344</v>
+        <v>1.034951550491964</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7395327847805908</v>
+        <v>1.019606203331319</v>
       </c>
       <c r="E5" s="4">
-        <v>84.00085034013607</v>
+        <v>71.6794217687073</v>
       </c>
       <c r="F5" s="4">
-        <v>73.77237136465322</v>
+        <v>59.22329418344503</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
         <v>6</v>
@@ -1796,9 +1972,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.034951550491964</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.507333863562924</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3154748409478676</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2003,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2022,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2064,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,107 +2095,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4628714525070474</v>
+        <v>0.3653631372020086</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3376572937861326</v>
+        <v>0.3752936043790452</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3817641009920191</v>
+        <v>0.4092503064487294</v>
       </c>
       <c r="E3" s="4">
-        <v>76.46447467876017</v>
+        <v>85.60468631897207</v>
       </c>
       <c r="F3" s="4">
-        <v>69.69115088242444</v>
+        <v>84.255530698482</v>
       </c>
       <c r="G3" s="5">
         <v>18</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3752936043790452</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1186682928636252</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1120339989946597</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4586338678094631</v>
+        <v>0.7989524991063961</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2221244798022072</v>
+        <v>0.3796275587593145</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3153869138684542</v>
+        <v>0.4308874009279463</v>
       </c>
       <c r="E4" s="4">
-        <v>74.96398559423783</v>
+        <v>79.0096038415371</v>
       </c>
       <c r="F4" s="4">
-        <v>62.57204895381113</v>
+        <v>71.78378734044063</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3796275587593145</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7028965727665131</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09313110577610831</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8010512513275194</v>
+        <v>0.6135847610860728</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7198172355488246</v>
+        <v>0.6446041548837099</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6640767615643433</v>
+        <v>0.6822487656906147</v>
       </c>
       <c r="E5" s="4">
-        <v>78.17602040816337</v>
+        <v>84.14115646258507</v>
       </c>
       <c r="F5" s="4">
-        <v>71.28495525727132</v>
+        <v>80.64387583892545</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
@@ -2001,17 +2264,35 @@
         <v>6</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.6438731366705339</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4408414679093151</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2790424416451491</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2303,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2322,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2364,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,25 +2395,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.35786959173095</v>
+        <v>0.4205360274305537</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1927150348217654</v>
+        <v>0.3597487605794202</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2673106938252066</v>
+        <v>0.4865530249734028</v>
       </c>
       <c r="E3" s="4">
-        <v>84.02494331065768</v>
+        <v>84.29705215419509</v>
       </c>
       <c r="F3" s="4">
-        <v>78.24011931394672</v>
+        <v>74.09209545115553</v>
       </c>
       <c r="G3" s="5">
         <v>18</v>
@@ -2126,48 +2440,66 @@
         <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3565388829557167</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.178385733252314</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1296322124739474</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8008817546647983</v>
+        <v>0.9071826894305722</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2963548845471058</v>
+        <v>0.507370411171842</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4247940115404005</v>
+        <v>0.5935208850388124</v>
       </c>
       <c r="E4" s="4">
-        <v>79.66386554621879</v>
+        <v>76.76070428171302</v>
       </c>
       <c r="F4" s="4">
-        <v>66.69298591920197</v>
+        <v>62.64903276746878</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>7</v>
@@ -2181,25 +2513,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4917416838715603</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8366889995040281</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.141660296360937</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7539629740924192</v>
+        <v>0.7690340203399706</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6487188798852721</v>
+        <v>0.7151851425864344</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6155829472007945</v>
+        <v>0.7395327847805908</v>
       </c>
       <c r="E5" s="4">
-        <v>81.15433673469381</v>
+        <v>84.00085034013607</v>
       </c>
       <c r="F5" s="4">
-        <v>78.87094519015672</v>
+        <v>73.77237136465322</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
@@ -2214,17 +2564,35 @@
         <v>6</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5452074508452334</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.55057959832629</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.435814399868939</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2603,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2611,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2622,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2664,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,107 +2695,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2363684189910141</v>
+        <v>0.4628714525070474</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2070871195236181</v>
+        <v>0.3376572937861326</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2408302425317306</v>
+        <v>0.3817641009920191</v>
       </c>
       <c r="E3" s="4">
-        <v>79.484126984127</v>
+        <v>76.46447467876017</v>
       </c>
       <c r="F3" s="4">
-        <v>82.66592095451115</v>
+        <v>69.69115088242444</v>
       </c>
       <c r="G3" s="5">
         <v>18</v>
       </c>
       <c r="H3" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3376572937861326</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2192933418848578</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1493494586064301</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3384855469404646</v>
+        <v>0.4586338678094631</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2326334792903696</v>
+        <v>0.2221244798022072</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3088111226086686</v>
+        <v>0.3153869138684542</v>
       </c>
       <c r="E4" s="4">
-        <v>76.0044017607043</v>
+        <v>74.96398559423783</v>
       </c>
       <c r="F4" s="4">
-        <v>71.86208711672595</v>
+        <v>62.57204895381113</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2090380132069387</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4254278837404727</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1509066338938695</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2861590830526391</v>
+        <v>0.8010512513275194</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1752472135232677</v>
+        <v>0.7198172355488246</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1891106670400446</v>
+        <v>0.6640767615643433</v>
       </c>
       <c r="E5" s="4">
-        <v>78.06972789115648</v>
+        <v>78.17602040816337</v>
       </c>
       <c r="F5" s="4">
-        <v>79.94267337807607</v>
+        <v>71.28495525727132</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
@@ -2427,17 +2864,35 @@
         <v>6</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3472565987632003</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.651562647921506</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6174951999753828</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2903,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2911,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2922,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2964,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,34 +2995,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2398930541407402</v>
+        <v>0.35786959173095</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1142263203374938</v>
+        <v>0.1927150348217654</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1681340906652409</v>
+        <v>0.2673106938252066</v>
       </c>
       <c r="E3" s="4">
-        <v>81.63832199546486</v>
+        <v>84.02494331065768</v>
       </c>
       <c r="F3" s="4">
-        <v>75.60899826000379</v>
+        <v>78.24011931394672</v>
       </c>
       <c r="G3" s="5">
         <v>18</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>5</v>
@@ -2566,81 +3054,117 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1340683369010319</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2925612074035133</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1554908395115719</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6777939886803641</v>
+        <v>0.8008817546647983</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2090065649754271</v>
+        <v>0.2963548845471058</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2243798582921958</v>
+        <v>0.4247940115404005</v>
       </c>
       <c r="E4" s="4">
-        <v>76.08643457382965</v>
+        <v>79.66386554621879</v>
       </c>
       <c r="F4" s="4">
-        <v>67.78720884327014</v>
+        <v>66.69298591920197</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2963548845471058</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.740901685979355</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2059415991589271</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5265031963020386</v>
+        <v>0.7539629740924192</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4358368540849598</v>
+        <v>0.6487188798852721</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4765509303365727</v>
+        <v>0.6155829472007945</v>
       </c>
       <c r="E5" s="4">
-        <v>82.82738095238093</v>
+        <v>81.15433673469381</v>
       </c>
       <c r="F5" s="4">
-        <v>78.65002796420582</v>
+        <v>78.87094519015672</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>5</v>
@@ -2648,9 +3172,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.437361850665544</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5798548854914569</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4562604425519564</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3203,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3211,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3222,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3264,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,34 +3295,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.248027952181147</v>
+        <v>0.2363684189910141</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2737397610688433</v>
+        <v>0.2070871195236181</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2995669301988375</v>
+        <v>0.2408302425317306</v>
       </c>
       <c r="E3" s="4">
-        <v>84.01738473167049</v>
+        <v>79.484126984127</v>
       </c>
       <c r="F3" s="4">
-        <v>81.83693760874826</v>
+        <v>82.66592095451115</v>
       </c>
       <c r="G3" s="5">
         <v>18</v>
       </c>
       <c r="H3" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>3</v>
@@ -2779,91 +3354,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1885787010160169</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1583481535305712</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1433542170492201</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3841412584113299</v>
+        <v>0.3384855469404646</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2393574835336868</v>
+        <v>0.2326334792903696</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3570095138787326</v>
+        <v>0.3088111226086686</v>
       </c>
       <c r="E4" s="4">
-        <v>79.73789515806324</v>
+        <v>76.0044017607043</v>
       </c>
       <c r="F4" s="4">
-        <v>72.40163179365739</v>
+        <v>71.86208711672595</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2326334792903696</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3071568799205562</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1286996975051355</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3380362017491842</v>
+        <v>0.2861590830526391</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3090227198988517</v>
+        <v>0.1752472135232677</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2783699336414648</v>
+        <v>0.1891106670400446</v>
       </c>
       <c r="E5" s="4">
-        <v>84.66624149659863</v>
+        <v>78.06972789115648</v>
       </c>
       <c r="F5" s="4">
-        <v>85.13422818791967</v>
+        <v>79.94267337807607</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1295718701356647</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2825726706566868</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1369027323176719</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3503,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3522,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3564,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,132 +3595,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2332854215425691</v>
+        <v>0.2398930541407402</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2218306780512323</v>
+        <v>0.1142263203374938</v>
       </c>
       <c r="D3" s="4">
-        <v>0.268632657821318</v>
+        <v>0.1681340906652409</v>
       </c>
       <c r="E3" s="4">
-        <v>79.181783824641</v>
+        <v>81.63832199546486</v>
       </c>
       <c r="F3" s="4">
-        <v>64.99502858563199</v>
+        <v>75.60899826000379</v>
       </c>
       <c r="G3" s="5">
         <v>18</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.02405777533859941</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2332010797381144</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1105123039350732</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4056105286098026</v>
+        <v>0.6777939886803641</v>
       </c>
       <c r="C4" s="4">
-        <v>0.09920961986617272</v>
+        <v>0.2090065649754271</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2132949954155157</v>
+        <v>0.2243798582921958</v>
       </c>
       <c r="E4" s="4">
-        <v>73.82352941176508</v>
+        <v>76.08643457382965</v>
       </c>
       <c r="F4" s="4">
-        <v>61.20147387814285</v>
+        <v>67.78720884327014</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2090065649754271</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5683146599611451</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1083912914719694</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5091053225134967</v>
+        <v>0.5265031963020386</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5066284138592899</v>
+        <v>0.4358368540849598</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5188110172996598</v>
+        <v>0.4765509303365727</v>
       </c>
       <c r="E5" s="4">
-        <v>80.23596938775511</v>
+        <v>82.82738095238093</v>
       </c>
       <c r="F5" s="4">
-        <v>67.0064317673378</v>
+        <v>78.65002796420582</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.430597772789734</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3597327057344631</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2344018076860013</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3803,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.248027952181147</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2737397610688433</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2995669301988375</v>
+      </c>
+      <c r="E3" s="4">
+        <v>84.01738473167049</v>
+      </c>
+      <c r="F3" s="4">
+        <v>81.83693760874826</v>
+      </c>
+      <c r="G3" s="5">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2163377459226461</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.176052766644181</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1755449178423264</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3841412584113299</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2393574835336868</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3570095138787326</v>
+      </c>
+      <c r="E4" s="4">
+        <v>79.73789515806324</v>
+      </c>
+      <c r="F4" s="4">
+        <v>72.40163179365739</v>
+      </c>
+      <c r="G4" s="5">
+        <v>17</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>5</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1764028202445065</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4043063059405436</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1990457643135319</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3380362017491842</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3090227198988517</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2783699336414648</v>
+      </c>
+      <c r="E5" s="4">
+        <v>84.66624149659863</v>
+      </c>
+      <c r="F5" s="4">
+        <v>85.13422818791967</v>
+      </c>
+      <c r="G5" s="5">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5">
+        <v>13</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.1247076504123066</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3279882021947597</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2870630550309209</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2332854215425691</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2218306780512323</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.268632657821318</v>
+      </c>
+      <c r="E3" s="4">
+        <v>79.181783824641</v>
+      </c>
+      <c r="F3" s="4">
+        <v>64.99502858563199</v>
+      </c>
+      <c r="G3" s="5">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>7</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2218306780512323</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.136332782843581</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1050284638833278</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4056105286098026</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.09920961986617272</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2132949954155157</v>
+      </c>
+      <c r="E4" s="4">
+        <v>73.82352941176508</v>
+      </c>
+      <c r="F4" s="4">
+        <v>61.20147387814285</v>
+      </c>
+      <c r="G4" s="5">
+        <v>17</v>
+      </c>
+      <c r="H4" s="5">
+        <v>8</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>9</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.04216150313173905</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4161064092300486</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1057028025097932</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.5091053225134967</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5066284138592899</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5188110172996598</v>
+      </c>
+      <c r="E5" s="4">
+        <v>80.23596938775511</v>
+      </c>
+      <c r="F5" s="4">
+        <v>67.0064317673378</v>
+      </c>
+      <c r="G5" s="5">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>7</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.5066284138592899</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3334224259244132</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.25466862529015</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>64.70588235294117</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>35.29411764705883</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.96078431372549</v>
+      </c>
+      <c r="F3" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4121619245357394</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2102066545736997</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1830773180769723</v>
+      </c>
+      <c r="K3" s="4">
+        <v>79.2703748165934</v>
+      </c>
+      <c r="L3" s="4">
+        <v>71.2569636355669</v>
+      </c>
+      <c r="M3" s="5">
+        <v>51</v>
+      </c>
+      <c r="N3" s="5">
+        <v>519096.4193344116</v>
+      </c>
+      <c r="O3" s="4">
+        <v>35.14532290686606</v>
+      </c>
+      <c r="P3" s="5">
+        <v>14770</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>64.70588235294117</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7.84313725490196</v>
+      </c>
+      <c r="D4" s="3">
+        <v>27.45098039215686</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>27.45098039215686</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.4868037848909239</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3513836867224794</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4582535131311906</v>
+      </c>
+      <c r="K4" s="4">
+        <v>76.35254101640651</v>
+      </c>
+      <c r="L4" s="4">
+        <v>66.64999780672865</v>
+      </c>
+      <c r="M4" s="5">
+        <v>51</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1132482.585430145</v>
+      </c>
+      <c r="O4" s="4">
+        <v>85.34799799759932</v>
+      </c>
+      <c r="P4" s="5">
+        <v>13269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>74.50980392156863</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3.92156862745098</v>
+      </c>
+      <c r="D5" s="3">
+        <v>21.56862745098039</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.92156862745098</v>
+      </c>
+      <c r="F5" s="3">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.4705664748317415</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2807825486936752</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.249037338520498</v>
+      </c>
+      <c r="K5" s="4">
+        <v>84.63251967453704</v>
+      </c>
+      <c r="L5" s="4">
+        <v>78.19055138834057</v>
+      </c>
+      <c r="M5" s="5">
+        <v>51</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2009877.454280853</v>
+      </c>
+      <c r="O5" s="4">
+        <v>141.5306988438035</v>
+      </c>
+      <c r="P5" s="5">
+        <v>14201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.96078431372549</v>
+      </c>
+      <c r="D6" s="3">
+        <v>31.37254901960784</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.92156862745098</v>
+      </c>
+      <c r="F6" s="3">
+        <v>27.45098039215686</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4392163811911393</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1618286907972795</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1983073355071153</v>
+      </c>
+      <c r="K6" s="4">
+        <v>81.38255302120875</v>
+      </c>
+      <c r="L6" s="4">
+        <v>74.7569855682766</v>
+      </c>
+      <c r="M6" s="5">
+        <v>51</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1617914.328098297</v>
+      </c>
+      <c r="O6" s="4">
+        <v>92.68528460691437</v>
+      </c>
+      <c r="P6" s="5">
+        <v>17456</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>70.58823529411765</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7.84313725490196</v>
+      </c>
+      <c r="D7" s="3">
+        <v>21.56862745098039</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="F7" s="3">
+        <v>15.68627450980392</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.302190590293873</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2092952929054376</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2146196666094722</v>
+      </c>
+      <c r="K7" s="4">
+        <v>85.78031212484994</v>
+      </c>
+      <c r="L7" s="4">
+        <v>79.28038777032083</v>
+      </c>
+      <c r="M7" s="5">
+        <v>51</v>
+      </c>
+      <c r="N7" s="5">
+        <v>5033968.827486038</v>
+      </c>
+      <c r="O7" s="4">
+        <v>347.1463228388413</v>
+      </c>
+      <c r="P7" s="5">
+        <v>14501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>49.01960784313725</v>
+      </c>
+      <c r="C8" s="3">
+        <v>7.84313725490196</v>
+      </c>
+      <c r="D8" s="3">
+        <v>43.13725490196079</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.96078431372549</v>
+      </c>
+      <c r="F8" s="3">
+        <v>41.17647058823529</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3395607540464864</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1505291786991264</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1970567276440209</v>
+      </c>
+      <c r="K8" s="4">
+        <v>75.74296385220761</v>
+      </c>
+      <c r="L8" s="4">
+        <v>57.6262227486057</v>
+      </c>
+      <c r="M8" s="5">
+        <v>51</v>
+      </c>
+      <c r="N8" s="5">
+        <v>376919.801235199</v>
+      </c>
+      <c r="O8" s="4">
+        <v>22.77048276658001</v>
+      </c>
+      <c r="P8" s="5">
+        <v>16553</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>41.17647058823529</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="D9" s="3">
+        <v>47.05882352941176</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="F9" s="3">
+        <v>41.17647058823529</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.6072420562062644</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3733197202145218</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.5244467673539011</v>
+      </c>
+      <c r="K9" s="4">
+        <v>69.13765506202481</v>
+      </c>
+      <c r="L9" s="4">
+        <v>56.87634337851442</v>
+      </c>
+      <c r="M9" s="5">
+        <v>51</v>
+      </c>
+      <c r="N9" s="5">
+        <v>596588.6831283569</v>
+      </c>
+      <c r="O9" s="4">
+        <v>34.86987451799386</v>
+      </c>
+      <c r="P9" s="5">
+        <v>17109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>72.54901960784314</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>27.45098039215686</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.92156862745098</v>
+      </c>
+      <c r="F10" s="3">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4144849901004907</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1515516368622497</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1863720854281606</v>
+      </c>
+      <c r="K10" s="4">
+        <v>82.94717887154881</v>
+      </c>
+      <c r="L10" s="4">
+        <v>78.96521472123756</v>
+      </c>
+      <c r="M10" s="5">
+        <v>51</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1660018.185853958</v>
+      </c>
+      <c r="O10" s="4">
+        <v>85.40506178185719</v>
+      </c>
+      <c r="P10" s="5">
+        <v>19437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>62.74509803921568</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>37.25490196078432</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>37.25490196078432</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.5145868581045249</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2290729222495665</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2585502998890994</v>
+      </c>
+      <c r="K11" s="4">
+        <v>81.69201013738812</v>
+      </c>
+      <c r="L11" s="4">
+        <v>70.17743562749554</v>
+      </c>
+      <c r="M11" s="5">
+        <v>51</v>
+      </c>
+      <c r="N11" s="5">
+        <v>558746.1543083191</v>
+      </c>
+      <c r="O11" s="4">
+        <v>48.04352143665684</v>
+      </c>
+      <c r="P11" s="5">
+        <v>11630</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>52.94117647058824</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.92156862745098</v>
+      </c>
+      <c r="D12" s="3">
+        <v>43.13725490196079</v>
+      </c>
+      <c r="E12" s="3">
+        <v>9.803921568627452</v>
+      </c>
+      <c r="F12" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4236187557697955</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.3231404823361191</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2546862607947759</v>
+      </c>
+      <c r="K12" s="4">
+        <v>76.50126717353625</v>
+      </c>
+      <c r="L12" s="4">
+        <v>67.8181339649954</v>
+      </c>
+      <c r="M12" s="5">
+        <v>51</v>
+      </c>
+      <c r="N12" s="5">
+        <v>360020.5881595612</v>
+      </c>
+      <c r="O12" s="4">
+        <v>26.26928771685963</v>
+      </c>
+      <c r="P12" s="5">
+        <v>13705</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>58.82352941176471</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="D13" s="3">
+        <v>35.29411764705883</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.96078431372549</v>
+      </c>
+      <c r="F13" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.5321393835838351</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2692009097643281</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2662127233804382</v>
+      </c>
+      <c r="K13" s="4">
+        <v>81.67066826730701</v>
+      </c>
+      <c r="L13" s="4">
+        <v>74.58898100627343</v>
+      </c>
+      <c r="M13" s="5">
+        <v>51</v>
+      </c>
+      <c r="N13" s="5">
+        <v>966160.7208251953</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.16560668704732</v>
+      </c>
+      <c r="P13" s="5">
+        <v>12685</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>68.62745098039215</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.96078431372549</v>
+      </c>
+      <c r="D14" s="3">
+        <v>29.41176470588236</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>29.41176470588236</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.2469234598569946</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.137323930113325</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1520950397006653</v>
+      </c>
+      <c r="K14" s="4">
+        <v>77.88048552754435</v>
+      </c>
+      <c r="L14" s="4">
+        <v>78.21029082774007</v>
+      </c>
+      <c r="M14" s="5">
+        <v>51</v>
+      </c>
+      <c r="N14" s="5">
+        <v>6288193.200588226</v>
+      </c>
+      <c r="O14" s="4">
+        <v>502.0914404813339</v>
+      </c>
+      <c r="P14" s="5">
+        <v>12524</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>68.62745098039215</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>31.37254901960784</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>31.37254901960784</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.384601802870136</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1487824011969608</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2022836215027826</v>
+      </c>
+      <c r="K15" s="4">
+        <v>80.16073095905027</v>
+      </c>
+      <c r="L15" s="4">
+        <v>73.95578365574394</v>
+      </c>
+      <c r="M15" s="5">
+        <v>51</v>
+      </c>
+      <c r="N15" s="5">
+        <v>5882067.153215408</v>
+      </c>
+      <c r="O15" s="4">
+        <v>515.8802975982642</v>
+      </c>
+      <c r="P15" s="5">
+        <v>11402</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>70.58823529411765</v>
+      </c>
+      <c r="C16" s="3">
+        <v>7.84313725490196</v>
+      </c>
+      <c r="D16" s="3">
+        <v>21.56862745098039</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>21.56862745098039</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.2998032987392285</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2216905678893425</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.2394459000845004</v>
+      </c>
+      <c r="K16" s="4">
+        <v>82.79445111377888</v>
+      </c>
+      <c r="L16" s="4">
+        <v>79.72627977365434</v>
+      </c>
+      <c r="M16" s="5">
+        <v>51</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1137669.828653336</v>
+      </c>
+      <c r="O16" s="4">
+        <v>106.9439583242466</v>
+      </c>
+      <c r="P16" s="5">
+        <v>10638</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>54.90196078431373</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>45.09803921568628</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>45.09803921568628</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2914227031938411</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1533197553716537</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.202589417120461</v>
+      </c>
+      <c r="K17" s="4">
+        <v>77.72642390289448</v>
+      </c>
+      <c r="L17" s="4">
+        <v>64.36153879896422</v>
+      </c>
+      <c r="M17" s="5">
+        <v>51</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1487499.842643738</v>
+      </c>
+      <c r="O17" s="4">
+        <v>111.4065190715801</v>
+      </c>
+      <c r="P17" s="5">
+        <v>13352</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>9</v>
@@ -3294,10 +5468,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -3338,10 +5512,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -3388,10 +5562,10 @@
         <v>7</v>
       </c>
       <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
         <v>3</v>
-      </c>
-      <c r="N7" s="5">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3429,13 +5603,13 @@
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -3473,13 +5647,13 @@
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3514,10 +5688,10 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L10" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -3605,13 +5779,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3646,10 +5820,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -3847,9 +6021,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5">
+        <v>14</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>14</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>38</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>9</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>9</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2</v>
+      </c>
+      <c r="F6" s="5">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5">
+        <v>11</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5">
+        <v>8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>3</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>7</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5">
+        <v>22</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>21</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>19</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>24</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5">
+        <v>21</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>20</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>37</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>14</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+      <c r="F10" s="5">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5">
+        <v>2</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>11</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>32</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>19</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>19</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>16</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>27</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>22</v>
+      </c>
+      <c r="E12" s="5">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5">
+        <v>17</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>5</v>
+      </c>
+      <c r="I12" s="5">
+        <v>3</v>
+      </c>
+      <c r="J12" s="5">
+        <v>3</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>8</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>30</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>18</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>17</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>10</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>35</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>15</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>11</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>35</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>16</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>16</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>13</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>36</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>11</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>11</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>11</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>28</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>23</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>23</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>16</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6789,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6831,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6862,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3757646815677502</v>
@@ -3960,10 +6921,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3799841475740373</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1451994073013083</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1089959684366049</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.8626930378081747</v>
@@ -4001,10 +6980,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.6917139626077009</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7351980916311021</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.185927371983899</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.7253774803814088</v>
@@ -4042,9 +7039,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.6596662145880338</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3692688288856518</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3660598291417237</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7070,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7089,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7131,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7162,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4799906482332301</v>
@@ -4173,10 +7221,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.495794973424636</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1345203058505488</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1183772610465317</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>2.647327437725156</v>
@@ -4214,10 +7280,28 @@
       <c r="M4" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>3.211991513385855</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.101467645120396</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9926806891968259</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.8411208396094714</v>
@@ -4255,9 +7339,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.8843122380012165</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2300423473175324</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2491345985677163</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7462,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3809155790482627</v>
@@ -4386,10 +7521,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3492951517812903</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2666815090549119</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1903024103175244</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6016335252913398</v>
@@ -4427,10 +7580,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2613017133969755</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5258494964821044</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1264032878260943</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.8077333005282958</v>
@@ -4468,9 +7639,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4971424113355424</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.641198850827164</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5353970441258131</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7762,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4086773710975433</v>
@@ -4599,10 +7821,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3909940215716442</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1630362556423747</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1310260190680909</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.8001718915262569</v>
@@ -4640,10 +7880,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.5212143024214747</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6688705693738481</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1235399229882823</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.7263502399160848</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.7192459530793677</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5059114474893709</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2432411990271406</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8062,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2924750753895332</v>
@@ -4812,10 +8121,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2770455694710837</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.17600239511501</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1870324434398843</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4815122797536175</v>
@@ -4853,10 +8180,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3286004229387526</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4205760655598921</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1721557489153838</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5666752702697813</v>
@@ -4894,9 +8239,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5586487562013792</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3183677423999486</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2589826612460704</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.376148285109726</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3492376250800563</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4205956319043509</v>
-      </c>
-      <c r="E3" s="4">
-        <v>76.43990929705224</v>
-      </c>
-      <c r="F3" s="4">
-        <v>58.23079791200577</v>
-      </c>
-      <c r="G3" s="5">
-        <v>18</v>
-      </c>
-      <c r="H3" s="5">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>7</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>7</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.7870588959260357</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6586366635667295</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.7045941021963328</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.45138055222137</v>
-      </c>
-      <c r="F4" s="4">
-        <v>54.75128306356228</v>
-      </c>
-      <c r="G4" s="5">
-        <v>17</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>7</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5693141169157028</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5806747116628879</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6077986728382027</v>
-      </c>
-      <c r="E5" s="4">
-        <v>77.39370748299307</v>
-      </c>
-      <c r="F5" s="4">
-        <v>60.00069910514471</v>
-      </c>
-      <c r="G5" s="5">
-        <v>16</v>
-      </c>
-      <c r="H5" s="5">
-        <v>8</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>8</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>7</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6158839136395208</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6342039573270242</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6923904223607664</v>
-      </c>
-      <c r="E3" s="4">
-        <v>71.15268329554043</v>
-      </c>
-      <c r="F3" s="4">
-        <v>60.75192642306679</v>
-      </c>
-      <c r="G3" s="5">
-        <v>18</v>
-      </c>
-      <c r="H3" s="5">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>8</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>8</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.086005537270964</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.102131863901128</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.078677262181763</v>
-      </c>
-      <c r="E4" s="4">
-        <v>64.61184473789527</v>
-      </c>
-      <c r="F4" s="4">
-        <v>50.56388998552374</v>
-      </c>
-      <c r="G4" s="5">
-        <v>17</v>
-      </c>
-      <c r="H4" s="5">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5">
-        <v>8</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>7</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.9158898097213899</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.034951550491964</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.019606203331319</v>
-      </c>
-      <c r="E5" s="4">
-        <v>71.6794217687073</v>
-      </c>
-      <c r="F5" s="4">
-        <v>59.22329418344503</v>
-      </c>
-      <c r="G5" s="5">
-        <v>16</v>
-      </c>
-      <c r="H5" s="5">
-        <v>8</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>8</v>
-      </c>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>6</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/BaeumerTuning2020.xlsx
+++ b/public/downloads/BaeumerTuning2020.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3394530233922035</v>
+        <v>0.3583918114659355</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1582858346731369</v>
+        <v>0.1521677665562221</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1446135462814576</v>
+        <v>0.1397672861102512</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -1616,13 +1616,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6586366635667295</v>
+        <v>0.6613235081801454</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5390914925380139</v>
+        <v>0.5401978403200087</v>
       </c>
       <c r="Q4" s="4">
         <v>0.09128535151654778</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5806747116628879</v>
+        <v>0.6156738592669879</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3314936286942565</v>
+        <v>0.3357693750469494</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2030960436603548</v>
+        <v>0.2028977494647155</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6342039573270242</v>
+        <v>0.5564420095770402</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2438838286614613</v>
+        <v>0.217305392630216</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2009519805218631</v>
+        <v>0.1752930900468826</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -1973,16 +1973,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>1.034951550491964</v>
+        <v>0.8993629708410644</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.507333863562924</v>
+        <v>0.4565698889514045</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3154748409478676</v>
+        <v>0.2817411815502782</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -2155,16 +2155,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3752936043790452</v>
+        <v>0.3607845269508516</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1186682928636252</v>
+        <v>0.1178454341951441</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1120339989946597</v>
+        <v>0.1111082829926184</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -2214,16 +2214,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3796275587593145</v>
+        <v>0.3619505368030147</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7028965727665131</v>
+        <v>0.697697448661719</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09313110577610831</v>
+        <v>0.09152410378008105</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6438731366705339</v>
+        <v>0.7185695615522754</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4408414679093151</v>
+        <v>0.4609941119299602</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2790424416451491</v>
+        <v>0.2664688171491365</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2455,16 +2455,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3565388829557167</v>
+        <v>0.4085831072265691</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.178385733252314</v>
+        <v>0.1649580836979112</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1296322124739474</v>
+        <v>0.1181647755208187</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4917416838715603</v>
+        <v>0.521914872795378</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8366889995040281</v>
+        <v>0.8449654220990372</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.141660296360937</v>
+        <v>0.1406436203105436</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -2573,16 +2573,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5452074508452334</v>
+        <v>0.7756433130688833</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.55057959832629</v>
+        <v>0.5396081024346935</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.435814399868939</v>
+        <v>0.3877319841767566</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2755,13 +2755,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3376572937861326</v>
+        <v>0.3653786884863166</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2192933418848578</v>
+        <v>0.2131330319514836</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1493494586064301</v>
@@ -2814,16 +2814,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2090380132069387</v>
+        <v>0.1973449184789615</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4254278837404727</v>
+        <v>0.4233643964355355</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1509066338938695</v>
+        <v>0.1492361917898728</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -2873,16 +2873,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3472565987632003</v>
+        <v>0.6175980007739099</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.651562647921506</v>
+        <v>0.6269916222235161</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6174951999753828</v>
+        <v>0.5943505913857429</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3055,16 +3055,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1340683369010319</v>
+        <v>0.1040667560180282</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2925612074035133</v>
+        <v>0.296108808569333</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1554908395115719</v>
+        <v>0.1508117142993003</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -3114,13 +3114,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2963548845471058</v>
+        <v>0.255728338706092</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.740901685979355</v>
+        <v>0.7432914827935323</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2059415991589271</v>
@@ -3173,16 +3173,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.437361850665544</v>
+        <v>0.5759762511254962</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5798548854914569</v>
+        <v>0.5684396299261416</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4562604425519564</v>
+        <v>0.4318084113505883</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1885787010160169</v>
+        <v>0.1668657055282528</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
@@ -3364,7 +3364,7 @@
         <v>0.1583481535305712</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1433542170492201</v>
+        <v>0.1419066840167025</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2326334792903696</v>
+        <v>0.1868786251490633</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3071568799205562</v>
+        <v>0.2945427992145966</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1286996975051355</v>
+        <v>0.1241574141261031</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -3473,13 +3473,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1295718701356647</v>
+        <v>0.1343630212233067</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2825726706566868</v>
+        <v>0.2837704584285973</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1369027323176719</v>
@@ -3655,16 +3655,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02405777533859941</v>
+        <v>0.03155407485689921</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2332010797381144</v>
+        <v>0.2315352354007144</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1105123039350732</v>
+        <v>0.1099356655105886</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3714,16 +3714,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2090065649754271</v>
+        <v>-0.1782156632048597</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5683146599611451</v>
+        <v>0.5695438572734028</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1083912914719694</v>
+        <v>0.1046926142689919</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -3773,16 +3773,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.430597772789734</v>
+        <v>0.5096919892429241</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3597327057344631</v>
+        <v>0.3519876382242875</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2344018076860013</v>
+        <v>0.2159458716300012</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -3955,16 +3955,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2163377459226461</v>
+        <v>0.2383014426817582</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.176052766644181</v>
+        <v>0.1753489719739264</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1755449178423264</v>
+        <v>0.1715023680149831</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -4014,16 +4014,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1764028202445065</v>
+        <v>0.1825140259004048</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4043063059405436</v>
+        <v>0.4053847539974668</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1990457643135319</v>
+        <v>0.1983667414628765</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -4073,16 +4073,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1247076504123066</v>
+        <v>0.1150738132582774</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3279882021947597</v>
+        <v>0.326783972550506</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2870630550309209</v>
+        <v>0.2863219906344572</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -4255,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2218306780512323</v>
+        <v>0.2439506789823085</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
@@ -4264,7 +4264,7 @@
         <v>0.136332782843581</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1050284638833278</v>
+        <v>0.1030175547077754</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -4314,16 +4314,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04216150313173905</v>
+        <v>-0.009581301648776019</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4161064092300486</v>
+        <v>0.4039197106717833</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1057028025097932</v>
+        <v>0.09920961986617272</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -4373,16 +4373,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5066284138592899</v>
+        <v>0.5615763454851503</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3334224259244132</v>
+        <v>0.3387344899563089</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.25466862529015</v>
+        <v>0.2485632995539433</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -4519,13 +4519,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4121619245357394</v>
+        <v>0.405304746570583</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2102066545736997</v>
+        <v>0.2065117734446817</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1830773180769723</v>
+        <v>0.1834453659569172</v>
       </c>
       <c r="K3" s="4">
         <v>79.2703748165934</v>
@@ -4569,13 +4569,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4868037848909239</v>
+        <v>0.4933030301670847</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3513836867224794</v>
+        <v>0.3463072220119945</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4582535131311906</v>
+        <v>0.4644747537958422</v>
       </c>
       <c r="K4" s="4">
         <v>76.35254101640651</v>
@@ -4619,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.4705664748317415</v>
+        <v>0.4681414504611806</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2807825486936752</v>
+        <v>0.2709655878993585</v>
       </c>
       <c r="J5" s="4">
-        <v>0.249037338520498</v>
+        <v>0.2560727397882583</v>
       </c>
       <c r="K5" s="4">
         <v>84.63251967453704</v>
@@ -4669,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4392163811911393</v>
+        <v>0.4359293523489225</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1618286907972795</v>
+        <v>0.1601553305666983</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1983073355071153</v>
+        <v>0.1984614633200108</v>
       </c>
       <c r="K6" s="4">
         <v>81.38255302120875</v>
@@ -4719,13 +4719,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.302190590293873</v>
+        <v>0.3089053943686754</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2092952929054376</v>
+        <v>0.2043443389493768</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2146196666094722</v>
+        <v>0.2134638162769977</v>
       </c>
       <c r="K7" s="4">
         <v>85.78031212484994</v>
@@ -4769,13 +4769,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3395607540464864</v>
+        <v>0.3391116291020262</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1505291786991264</v>
+        <v>0.148333370081191</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1970567276440209</v>
+        <v>0.1950949347097054</v>
       </c>
       <c r="K8" s="4">
         <v>75.74296385220761</v>
@@ -4819,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6072420562062644</v>
+        <v>0.581935478905348</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3733197202145218</v>
+        <v>0.3482502830749731</v>
       </c>
       <c r="J9" s="4">
-        <v>0.5244467673539011</v>
+        <v>0.5249601205325185</v>
       </c>
       <c r="K9" s="4">
         <v>69.13765506202481</v>
@@ -4869,13 +4869,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4144849901004907</v>
+        <v>0.418783926149827</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1515516368622497</v>
+        <v>0.1472752929987609</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1863720854281606</v>
+        <v>0.1830966962278059</v>
       </c>
       <c r="K10" s="4">
         <v>82.94717887154881</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.5145868581045249</v>
+        <v>0.5091644572784535</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2290729222495665</v>
+        <v>0.2094291672225883</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2585502998890994</v>
+        <v>0.2433415007407692</v>
       </c>
       <c r="K11" s="4">
         <v>81.69201013738812</v>
@@ -4969,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4236187557697955</v>
+        <v>0.4130481425511189</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3231404823361191</v>
+        <v>0.3141353274981792</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2546862607947759</v>
+        <v>0.2292024067202783</v>
       </c>
       <c r="K12" s="4">
         <v>76.50126717353625</v>
@@ -5019,13 +5019,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.5321393835838351</v>
+        <v>0.5306068204030648</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2692009097643281</v>
+        <v>0.2591785826122968</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2662127233804382</v>
+        <v>0.2501141661257407</v>
       </c>
       <c r="K13" s="4">
         <v>81.67066826730701</v>
@@ -5069,13 +5069,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.2469234598569946</v>
+        <v>0.2430945428442349</v>
       </c>
       <c r="I14" s="4">
-        <v>0.137323930113325</v>
+        <v>0.1354057635625225</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1520950397006653</v>
+        <v>0.1553814694133342</v>
       </c>
       <c r="K14" s="4">
         <v>77.88048552754435</v>
@@ -5119,13 +5119,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.384601802870136</v>
+        <v>0.3819937651460648</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1487824011969608</v>
+        <v>0.1416053427579022</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2022836215027826</v>
+        <v>0.1981486099587385</v>
       </c>
       <c r="K15" s="4">
         <v>80.16073095905027</v>
@@ -5169,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.2998032987392285</v>
+        <v>0.2995365857705041</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2216905678893425</v>
+        <v>0.2196811028784332</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2394459000845004</v>
+        <v>0.2373664371397969</v>
       </c>
       <c r="K16" s="4">
         <v>82.79445111377888</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2914227031938411</v>
+        <v>0.2890270002334455</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1533197553716537</v>
+        <v>0.1487121341678715</v>
       </c>
       <c r="J17" s="4">
-        <v>0.202589417120461</v>
+        <v>0.2075291008625516</v>
       </c>
       <c r="K17" s="4">
         <v>77.72642390289448</v>
@@ -6922,16 +6922,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3799841475740373</v>
+        <v>0.3599058836389304</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1451994073013083</v>
+        <v>0.1420335499164251</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1089959684366049</v>
+        <v>0.1061569554371595</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -6981,16 +6981,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6917139626077009</v>
+        <v>0.6438828116002924</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7351980916311021</v>
+        <v>0.7105015054360041</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.185927371983899</v>
+        <v>0.1774249811574187</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -7040,13 +7040,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6596662145880338</v>
+        <v>0.7232218755988242</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3692688288856518</v>
+        <v>0.3772132865120006</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3660598291417237</v>
@@ -7222,16 +7222,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.495794973424636</v>
+        <v>0.5247124263174214</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1345203058505488</v>
+        <v>0.1350957951833378</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1183772610465317</v>
+        <v>0.1149861112040053</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -7281,16 +7281,16 @@
         <v>5</v>
       </c>
       <c r="N4" s="4">
-        <v>3.211991513385855</v>
+        <v>3.289818297846686</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>1.101467645120396</v>
+        <v>1.127992054148391</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.9926806891968259</v>
+        <v>0.9815625771309929</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -7340,16 +7340,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8843122380012165</v>
+        <v>0.8475142085937932</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2300423473175324</v>
+        <v>0.2219290815436614</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2491345985677163</v>
+        <v>0.2456162274685661</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -7522,16 +7522,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3492951517812903</v>
+        <v>0.276088641855381</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2666815090549119</v>
+        <v>0.2528306056144669</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1903024103175244</v>
+        <v>0.1785617601840509</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -7581,16 +7581,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2613017133969755</v>
+        <v>0.2372252737860663</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5258494964821044</v>
+        <v>0.5202317745839525</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1264032878260943</v>
+        <v>0.1220988884582067</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -7640,16 +7640,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4971424113355424</v>
+        <v>0.6825062395521222</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.641198850827164</v>
+        <v>0.6550201815332883</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5353970441258131</v>
+        <v>0.5229315136978823</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -7822,13 +7822,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3909940215716442</v>
+        <v>0.3792605409075804</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1630362556423747</v>
+        <v>0.1643399757161595</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1310260190680909</v>
@@ -7881,13 +7881,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5212143024214747</v>
+        <v>0.5245058691363056</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6688705693738481</v>
+        <v>0.6698386772311513</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1235399229882823</v>
@@ -7940,16 +7940,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7192459530793677</v>
+        <v>0.6815786985754748</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5059114474893709</v>
+        <v>0.4929387433734127</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2432411990271406</v>
+        <v>0.2375517742431647</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -8122,16 +8122,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2770455694710837</v>
+        <v>0.2559805107238731</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.17600239511501</v>
+        <v>0.1760034594726526</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1870324434398843</v>
+        <v>0.1840245177929662</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3286004229387526</v>
+        <v>0.4530434265562917</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4205760655598921</v>
+        <v>0.442536595610046</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1721557489153838</v>
+        <v>0.1583287485134351</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -8240,16 +8240,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5586487562013792</v>
+        <v>0.5469683764575848</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3183677423999486</v>
+        <v>0.3164369198077446</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2589826612460704</v>
+        <v>0.2580841704965478</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
